--- a/docs/downloads/20261001_Ukay_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/20261001_Ukay_Teduh_Weekly_Update.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:X22"/>
+  <dimension ref="A2:AA22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,10 @@
     <col width="9" customWidth="1" min="21" max="21"/>
     <col width="9" customWidth="1" min="22" max="22"/>
     <col width="9" customWidth="1" min="23" max="23"/>
-    <col width="46" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="46" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -545,8 +548,11 @@
       <c r="R3" s="3" t="n">
         <v>46283</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="3" t="n">
         <v>46290</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>46297</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -652,22 +658,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="U4" s="6" t="inlineStr">
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="V4" s="6" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="W4" s="6" t="inlineStr">
+      <c r="W4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="X4" s="5" t="inlineStr">
+      <c r="X4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="Y4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="Z4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -745,18 +766,29 @@
         <f>S5/$D$5</f>
         <v/>
       </c>
-      <c r="U5" s="12">
+      <c r="U5" s="10">
         <f>V5-S5</f>
         <v/>
       </c>
-      <c r="V5" s="12" t="n">
+      <c r="V5" s="10" t="n">
         <v>98</v>
       </c>
-      <c r="W5" s="13">
+      <c r="W5" s="11">
         <f>V5/$D$5</f>
         <v/>
       </c>
-      <c r="X5" s="8" t="inlineStr">
+      <c r="X5" s="12">
+        <f>Y5-V5</f>
+        <v/>
+      </c>
+      <c r="Y5" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="Z5" s="13">
+        <f>Y5/$D$5</f>
+        <v/>
+      </c>
+      <c r="AA5" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block A: 57 units, Block B: 41 units</t>
         </is>
@@ -834,20 +866,31 @@
         <f>S6/$D$6</f>
         <v/>
       </c>
-      <c r="U6" s="12">
+      <c r="U6" s="10">
         <f>V6-S6</f>
         <v/>
       </c>
-      <c r="V6" s="12" t="n">
+      <c r="V6" s="10" t="n">
         <v>350</v>
       </c>
-      <c r="W6" s="13">
+      <c r="W6" s="11">
         <f>V6/$D$6</f>
         <v/>
       </c>
-      <c r="X6" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A1: 45 units, Block A2: 204 units, Block B: 101 units</t>
+      <c r="X6" s="12">
+        <f>Y6-V6</f>
+        <v/>
+      </c>
+      <c r="Y6" s="12" t="n">
+        <v>352</v>
+      </c>
+      <c r="Z6" s="13">
+        <f>Y6/$D$6</f>
+        <v/>
+      </c>
+      <c r="AA6" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A1: 47 units, Block A2: 204 units, Block B: 101 units</t>
         </is>
       </c>
     </row>
@@ -884,10 +927,13 @@
       <c r="R7" s="10" t="n"/>
       <c r="S7" s="10" t="n"/>
       <c r="T7" s="11" t="n"/>
-      <c r="U7" s="12" t="n"/>
-      <c r="V7" s="12" t="n"/>
-      <c r="W7" s="13" t="n"/>
-      <c r="X7" s="8" t="inlineStr">
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="10" t="n"/>
+      <c r="W7" s="11" t="n"/>
+      <c r="X7" s="12" t="n"/>
+      <c r="Y7" s="12" t="n"/>
+      <c r="Z7" s="13" t="n"/>
+      <c r="AA7" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
@@ -926,10 +972,13 @@
       <c r="R8" s="10" t="n"/>
       <c r="S8" s="10" t="n"/>
       <c r="T8" s="11" t="n"/>
-      <c r="U8" s="12" t="n"/>
-      <c r="V8" s="12" t="n"/>
-      <c r="W8" s="13" t="n"/>
-      <c r="X8" s="8" t="inlineStr">
+      <c r="U8" s="10" t="n"/>
+      <c r="V8" s="10" t="n"/>
+      <c r="W8" s="11" t="n"/>
+      <c r="X8" s="12" t="n"/>
+      <c r="Y8" s="12" t="n"/>
+      <c r="Z8" s="13" t="n"/>
+      <c r="AA8" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
@@ -1007,18 +1056,29 @@
         <f>S9/$D$9</f>
         <v/>
       </c>
-      <c r="U9" s="12">
+      <c r="U9" s="10">
         <f>V9-S9</f>
         <v/>
       </c>
-      <c r="V9" s="12" t="n">
+      <c r="V9" s="10" t="n">
         <v>342</v>
       </c>
-      <c r="W9" s="13">
+      <c r="W9" s="11">
         <f>V9/$D$9</f>
         <v/>
       </c>
-      <c r="X9" s="8" t="inlineStr">
+      <c r="X9" s="12">
+        <f>Y9-V9</f>
+        <v/>
+      </c>
+      <c r="Y9" s="12" t="n">
+        <v>342</v>
+      </c>
+      <c r="Z9" s="13">
+        <f>Y9/$D$9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block L: 342 units</t>
         </is>
@@ -1096,18 +1156,29 @@
         <f>S10/$D$10</f>
         <v/>
       </c>
-      <c r="U10" s="12">
+      <c r="U10" s="10">
         <f>V10-S10</f>
         <v/>
       </c>
-      <c r="V10" s="12" t="n">
+      <c r="V10" s="10" t="n">
         <v>228</v>
       </c>
-      <c r="W10" s="13">
+      <c r="W10" s="11">
         <f>V10/$D$10</f>
         <v/>
       </c>
-      <c r="X10" s="8" t="inlineStr"/>
+      <c r="X10" s="12">
+        <f>Y10-V10</f>
+        <v/>
+      </c>
+      <c r="Y10" s="12" t="n">
+        <v>228</v>
+      </c>
+      <c r="Z10" s="13">
+        <f>Y10/$D$10</f>
+        <v/>
+      </c>
+      <c r="AA10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1181,18 +1252,29 @@
         <f>S11/$D$11</f>
         <v/>
       </c>
-      <c r="U11" s="12">
+      <c r="U11" s="10">
         <f>V11-S11</f>
         <v/>
       </c>
-      <c r="V11" s="12" t="n">
+      <c r="V11" s="10" t="n">
         <v>273</v>
       </c>
-      <c r="W11" s="13">
+      <c r="W11" s="11">
         <f>V11/$D$11</f>
         <v/>
       </c>
-      <c r="X11" s="8" t="inlineStr"/>
+      <c r="X11" s="12">
+        <f>Y11-V11</f>
+        <v/>
+      </c>
+      <c r="Y11" s="12" t="n">
+        <v>273</v>
+      </c>
+      <c r="Z11" s="13">
+        <f>Y11/$D$11</f>
+        <v/>
+      </c>
+      <c r="AA11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1266,18 +1348,29 @@
         <f>S12/$D$12</f>
         <v/>
       </c>
-      <c r="U12" s="12">
+      <c r="U12" s="10">
         <f>V12-S12</f>
         <v/>
       </c>
-      <c r="V12" s="12" t="n">
+      <c r="V12" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="W12" s="13">
+      <c r="W12" s="11">
         <f>V12/$D$12</f>
         <v/>
       </c>
-      <c r="X12" s="8" t="inlineStr">
+      <c r="X12" s="12">
+        <f>Y12-V12</f>
+        <v/>
+      </c>
+      <c r="Y12" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z12" s="13">
+        <f>Y12/$D$12</f>
+        <v/>
+      </c>
+      <c r="AA12" s="8" t="inlineStr">
         <is>
           <t>Phase 1, completed Dec 2016</t>
         </is>
@@ -1339,18 +1432,29 @@
         <f>S13/$D$13</f>
         <v/>
       </c>
-      <c r="U13" s="12">
+      <c r="U13" s="10">
         <f>V13-S13</f>
         <v/>
       </c>
-      <c r="V13" s="12" t="n">
+      <c r="V13" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="W13" s="13">
+      <c r="W13" s="11">
         <f>V13/$D$13</f>
         <v/>
       </c>
-      <c r="X13" s="8" t="inlineStr">
+      <c r="X13" s="12">
+        <f>Y13-V13</f>
+        <v/>
+      </c>
+      <c r="Y13" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z13" s="13">
+        <f>Y13/$D$13</f>
+        <v/>
+      </c>
+      <c r="AA13" s="8" t="inlineStr">
         <is>
           <t>First 16 units on TEDUH (registered as Embun); remaining 36 units not yet launched</t>
         </is>
@@ -1428,18 +1532,29 @@
         <f>S14/$D$14</f>
         <v/>
       </c>
-      <c r="U14" s="12">
+      <c r="U14" s="10">
         <f>V14-S14</f>
         <v/>
       </c>
-      <c r="V14" s="12" t="n">
+      <c r="V14" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="W14" s="13">
+      <c r="W14" s="11">
         <f>V14/$D$14</f>
         <v/>
       </c>
-      <c r="X14" s="8" t="inlineStr"/>
+      <c r="X14" s="12">
+        <f>Y14-V14</f>
+        <v/>
+      </c>
+      <c r="Y14" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="Z14" s="13">
+        <f>Y14/$D$14</f>
+        <v/>
+      </c>
+      <c r="AA14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1513,18 +1628,29 @@
         <f>S15/$D$15</f>
         <v/>
       </c>
-      <c r="U15" s="12">
+      <c r="U15" s="10">
         <f>V15-S15</f>
         <v/>
       </c>
-      <c r="V15" s="12" t="n">
+      <c r="V15" s="10" t="n">
         <v>222</v>
       </c>
-      <c r="W15" s="13">
+      <c r="W15" s="11">
         <f>V15/$D$15</f>
         <v/>
       </c>
-      <c r="X15" s="8" t="inlineStr"/>
+      <c r="X15" s="12">
+        <f>Y15-V15</f>
+        <v/>
+      </c>
+      <c r="Y15" s="12" t="n">
+        <v>222</v>
+      </c>
+      <c r="Z15" s="13">
+        <f>Y15/$D$15</f>
+        <v/>
+      </c>
+      <c r="AA15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1598,18 +1724,29 @@
         <f>S16/$D$16</f>
         <v/>
       </c>
-      <c r="U16" s="12">
+      <c r="U16" s="10">
         <f>V16-S16</f>
         <v/>
       </c>
-      <c r="V16" s="12" t="n">
+      <c r="V16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="13">
+      <c r="W16" s="11">
         <f>V16/$D$16</f>
         <v/>
       </c>
-      <c r="X16" s="8" t="inlineStr">
+      <c r="X16" s="12">
+        <f>Y16-V16</f>
+        <v/>
+      </c>
+      <c r="Y16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="13">
+        <f>Y16/$D$16</f>
+        <v/>
+      </c>
+      <c r="AA16" s="8" t="inlineStr">
         <is>
           <t>No unit found on TEDUH</t>
         </is>
@@ -1687,18 +1824,29 @@
         <f>S17/$D$17</f>
         <v/>
       </c>
-      <c r="U17" s="12">
+      <c r="U17" s="10">
         <f>V17-S17</f>
         <v/>
       </c>
-      <c r="V17" s="12" t="n">
+      <c r="V17" s="10" t="n">
         <v>197</v>
       </c>
-      <c r="W17" s="13">
+      <c r="W17" s="11">
         <f>V17/$D$17</f>
         <v/>
       </c>
-      <c r="X17" s="8" t="inlineStr">
+      <c r="X17" s="12">
+        <f>Y17-V17</f>
+        <v/>
+      </c>
+      <c r="Y17" s="12" t="n">
+        <v>197</v>
+      </c>
+      <c r="Z17" s="13">
+        <f>Y17/$D$17</f>
+        <v/>
+      </c>
+      <c r="AA17" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block B: 197 units</t>
         </is>
@@ -1776,18 +1924,29 @@
         <f>S18/$D$18</f>
         <v/>
       </c>
-      <c r="U18" s="12">
+      <c r="U18" s="10">
         <f>V18-S18</f>
         <v/>
       </c>
-      <c r="V18" s="12" t="n">
+      <c r="V18" s="10" t="n">
         <v>81</v>
       </c>
-      <c r="W18" s="13">
+      <c r="W18" s="11">
         <f>V18/$D$18</f>
         <v/>
       </c>
-      <c r="X18" s="8" t="inlineStr"/>
+      <c r="X18" s="12">
+        <f>Y18-V18</f>
+        <v/>
+      </c>
+      <c r="Y18" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z18" s="13">
+        <f>Y18/$D$18</f>
+        <v/>
+      </c>
+      <c r="AA18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -1861,18 +2020,29 @@
         <f>S19/$D$19</f>
         <v/>
       </c>
-      <c r="U19" s="12">
+      <c r="U19" s="10">
         <f>V19-S19</f>
         <v/>
       </c>
-      <c r="V19" s="12" t="n">
+      <c r="V19" s="10" t="n">
         <v>456</v>
       </c>
-      <c r="W19" s="13">
+      <c r="W19" s="11">
         <f>V19/$D$19</f>
         <v/>
       </c>
-      <c r="X19" s="8" t="inlineStr">
+      <c r="X19" s="12">
+        <f>Y19-V19</f>
+        <v/>
+      </c>
+      <c r="Y19" s="12" t="n">
+        <v>456</v>
+      </c>
+      <c r="Z19" s="13">
+        <f>Y19/$D$19</f>
+        <v/>
+      </c>
+      <c r="AA19" s="8" t="inlineStr">
         <is>
           <t>Latest sales - Block A1: 223 units, Block A2: 233 units</t>
         </is>
@@ -1950,18 +2120,29 @@
         <f>S20/$D$20</f>
         <v/>
       </c>
-      <c r="U20" s="12">
+      <c r="U20" s="10">
         <f>V20-S20</f>
         <v/>
       </c>
-      <c r="V20" s="12" t="n">
+      <c r="V20" s="10" t="n">
         <v>104</v>
       </c>
-      <c r="W20" s="13">
+      <c r="W20" s="11">
         <f>V20/$D$20</f>
         <v/>
       </c>
-      <c r="X20" s="8" t="inlineStr"/>
+      <c r="X20" s="12">
+        <f>Y20-V20</f>
+        <v/>
+      </c>
+      <c r="Y20" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="Z20" s="13">
+        <f>Y20/$D$20</f>
+        <v/>
+      </c>
+      <c r="AA20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -2035,18 +2216,29 @@
         <f>S21/$D$21</f>
         <v/>
       </c>
-      <c r="U21" s="12">
+      <c r="U21" s="10">
         <f>V21-S21</f>
         <v/>
       </c>
-      <c r="V21" s="12" t="n">
+      <c r="V21" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="W21" s="13">
+      <c r="W21" s="11">
         <f>V21/$D$21</f>
         <v/>
       </c>
-      <c r="X21" s="8" t="inlineStr"/>
+      <c r="X21" s="12">
+        <f>Y21-V21</f>
+        <v/>
+      </c>
+      <c r="Y21" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z21" s="13">
+        <f>Y21/$D$21</f>
+        <v/>
+      </c>
+      <c r="AA21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2077,19 +2269,23 @@
       <c r="R22" s="10" t="n"/>
       <c r="S22" s="10" t="n"/>
       <c r="T22" s="11" t="n"/>
-      <c r="U22" s="12" t="n"/>
-      <c r="V22" s="12" t="n"/>
-      <c r="W22" s="13" t="n"/>
-      <c r="X22" s="8" t="inlineStr">
+      <c r="U22" s="10" t="n"/>
+      <c r="V22" s="10" t="n"/>
+      <c r="W22" s="11" t="n"/>
+      <c r="X22" s="12" t="n"/>
+      <c r="Y22" s="12" t="n"/>
+      <c r="Z22" s="13" t="n"/>
+      <c r="AA22" s="8" t="inlineStr">
         <is>
           <t>No TEDUH code</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="U3:W3"/>
+    <mergeCell ref="X3:Z3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="L3:N3"/>
